--- a/test_data/workshop_data.xlsx
+++ b/test_data/workshop_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tom\Documents\GitHub\GRG23VBS-Berufsorientierungstage-Zuteilung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tom\Documents\GitHub\GRG23VBS-Berufsorientierungstage-Zuteilung\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6B912E-30B5-46CB-9811-FF2A58B8DD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A4CDC2-18AA-4450-AC51-CEBFBF7F6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3398" yWindow="8002" windowWidth="20716" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,8 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -385,17 +384,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -411,7 +410,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>20</v>
       </c>
     </row>
@@ -419,7 +418,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>20</v>
       </c>
     </row>
@@ -427,7 +426,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>20</v>
       </c>
     </row>
@@ -435,7 +434,7 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>20</v>
       </c>
     </row>
@@ -443,47 +442,41 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="B11">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
